--- a/stories/arbres/ATOM-SOC.ARG.001-07.xlsx
+++ b/stories/arbres/ATOM-SOC.ARG.001-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Ce matin, papa a fini son travail. Il rentre avec son sac. Coralie l'attend près de la porte. Papa dit : j'ai travaillé. Avec le travail, on a de l'argent. L'argent sert à acheter. Coralie et papa vont au marché. D'abord, le stand du pain. Papa donne l'argent. Il peut acheter du pain. Coralie porte la baguette tiède. Ensuite, les légumes. Des poireaux. Des tomates. Papa dit : l'argent sert aussi aux légumes. Coralie pose une tomate dans le cabas. Plus loin, il y a des chaussures. Papa montre une paire. Il dit : l'argent sert aux chaussures, quand on en a besoin. Coralie touche le cuir souple. Papa range le reste. Coralie dit : le travail de papa sert à acheter pain légumes chaussures. L'argent ne pousse pas tout seul.</t>
+          <t>Ce matin, papa a fini son travail. Il rentre avec son sac. Coralie l'attend près de la porte. J'ai travaillé. Avec le travail, on a de l'argent. L'argent sert à acheter. Coralie et papa vont au marché. D'abord, le stand du pain. Papa donne l'argent. Il peut acheter du pain. Coralie porte la baguette tiède. Ensuite, les légumes. Des poireaux. Des tomates. L'argent sert aussi aux légumes. Coralie pose une tomate dans le cabas. Plus loin, il y a des chaussures. Papa montre une paire. L'argent sert aux chaussures, quand on en a besoin. Coralie touche le cuir souple. Papa range le reste. Le travail de papa sert à acheter pain légumes chaussures. L'argent ne pousse pas tout seul.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,18 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Ce matin, papa a fini son travail. Il rentre avec son sac. Coralie l'attend près de la porte.
+papa|J'ai travaillé. Avec le travail, on a de l'argent. L'argent sert à acheter.
+narrateur|Coralie et papa vont au marché. D'abord, le stand du pain. Papa donne l'argent. Il peut acheter du pain. Coralie porte la baguette tiède. Ensuite, les légumes. Des poireaux. Des tomates.
+papa|L'argent sert aussi aux légumes.
+narrateur|Coralie pose une tomate dans le cabas. Plus loin, il y a des chaussures. Papa montre une paire.
+narrateur|L'argent sert aux chaussures, quand on en a besoin.
+narrateur|Coralie touche le cuir souple. Papa range le reste.
+enfant-f|Le travail de papa sert à acheter pain légumes chaussures. L'argent ne pousse pas tout seul.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1497,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Papa a travaillé. L'argent sert à quoi ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1670,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Coralie a compris. Le travail de papa sert. L'argent sert à acheter. Pain. Légumes. Chaussures.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1833,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|À la maison, Coralie pose le pain. Papa range les légumes.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +2000,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2040,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.ARG.001-07.xlsx
+++ b/stories/arbres/ATOM-SOC.ARG.001-07.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1317,6 +1322,7 @@
 enfant-f|Le travail de papa sert à acheter pain légumes chaussures. L'argent ne pousse pas tout seul.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1504,6 +1510,7 @@
           <t>narrateur|Papa a travaillé. L'argent sert à quoi ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1675,6 +1682,7 @@
           <t>narrateur|Coralie a compris. Le travail de papa sert. L'argent sert à acheter. Pain. Légumes. Chaussures.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1838,6 +1846,7 @@
           <t>narrateur|À la maison, Coralie pose le pain. Papa range les légumes.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2005,6 +2014,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2023,7 +2033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2047,6 +2057,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2248,6 +2272,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SOC.ARG.001-07.xlsx
+++ b/stories/arbres/ATOM-SOC.ARG.001-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Coralie et l'argent du marché</t>
+          <t>Le fromage doux d'Aniss</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Aniss et papa vont au marché couvert avec l'argent du travail. Le fromage fort pique. Ils prennent le doux. Aniss le tient.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Ce matin, papa a fini son travail. Il rentre avec son sac. Coralie l'attend près de la porte. J'ai travaillé. Avec le travail, on a de l'argent. L'argent sert à acheter. Coralie et papa vont au marché. D'abord, le stand du pain. Papa donne l'argent. Il peut acheter du pain. Coralie porte la baguette tiède. Ensuite, les légumes. Des poireaux. Des tomates. L'argent sert aussi aux légumes. Coralie pose une tomate dans le cabas. Plus loin, il y a des chaussures. Papa montre une paire. L'argent sert aux chaussures, quand on en a besoin. Coralie touche le cuir souple. Papa range le reste. Le travail de papa sert à acheter pain légumes chaussures. L'argent ne pousse pas tout seul.</t>
+          <t>Les vitres du hall font des carreaux d'or. Des pigeons marchent sur une poutre. Ça sent le foin et le lait. Une paille craque sous une caisse. Le toit de verre cliquette un peu. Papa a fini son travail. Sa poche de toile est lourde. J'ai travaillé, Aniss. Avec le travail, on a de l'argent. L'argent sert à acheter. On achète du fromage ? Oui. Pour le pain de ce soir. En ce moment, ils marchent sous le verre. Aniss tient le bord du cabas. Le cabas gratte un peu sa jambe. Un stand aligne des meules. Des croûtes jaunes brillent. Ça sent fort ! Tu as senti le fromage ? Aniss se penche vers une meule. La croûte est rêche sous son doigt. Je veux celui-là. Papa coupe un tout petit bout. Aniss goûte. Le goût pique sa langue. Il est trop fort ! Il pique, n'est-ce pas ? Aniss recule d'un pas. Ses yeux piquent un peu. Je n'en veux plus. On prend le doux, alors ? À côté, une meule est plus claire. Elle sent le lait, presque rien. Celle-là. Elle est douce. Tu la veux pour le pain ? Oui, papa. Papa sort l'argent de sa poche. Les pièces sont froides et claires. C'est l'argent du travail. Il sert à acheter.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Ce matin, papa a fini son &lt;emphasis level="moderate"&gt;travail&lt;/emphasis&gt;. Il rentre avec son sac. Coralie l'attend près de la porte. Papa dit : j'ai travaillé. Avec le travail, on a de l'argent. L'argent sert à acheter. Coralie et papa vont au marché. D'abord, le stand du pain. Papa donne l'argent. Il peut acheter du pain. Coralie porte la baguette tiède. Ensuite, les légumes. Des poireaux. Des tomates. Papa dit : l'argent sert aussi aux légumes. Coralie pose une tomate dans le cabas. Plus loin, il y a des chaussures. Papa montre une paire. Il dit : l'argent sert aux chaussures, quand on en a besoin. Coralie touche le cuir souple. Papa range le reste. Coralie dit : le travail de papa sert à acheter pain légumes chaussures. L'argent ne pousse pas tout seul.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Les vitres du hall font des carreaux d'or. Des pigeons marchent sur une poutre. Ça sent le foin et le lait. Une paille craque sous une caisse. Le toit de verre cliquette un peu. Papa a fini son travail. Sa poche de toile est lourde. J'ai travaillé, Aniss. Avec le travail, on a de l'argent. L'argent sert à acheter. On achète du fromage ? Oui. Pour le pain de ce soir. En ce moment, ils marchent sous le verre. Aniss tient le bord du cabas. Le cabas gratte un peu sa jambe. Un stand aligne des meules. Des croûtes jaunes brillent. Ça sent fort ! Tu as senti le fromage ? Aniss se penche vers une meule. La croûte est rêche sous son doigt. Je veux celui-là. Papa coupe un tout petit bout. Aniss goûte. Le goût pique sa langue. Il est trop fort ! Il pique, n'est-ce pas ? Aniss recule d'un pas. Ses yeux piquent un peu. Je n'en veux plus. On prend le doux, alors ? À côté, une meule est plus claire. Elle sent le lait, presque rien. Celle-là. Elle est douce. Tu la veux pour le pain ? Oui, papa. Papa sort l'argent de sa poche. Les pièces sont froides et claires. C'est l'argent du travail. Il sert à acheter.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.96</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,17 +1324,50 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Ce matin, papa a fini son travail. Il rentre avec son sac. Coralie l'attend près de la porte.
-papa|J'ai travaillé. Avec le travail, on a de l'argent. L'argent sert à acheter.
-narrateur|Coralie et papa vont au marché. D'abord, le stand du pain. Papa donne l'argent. Il peut acheter du pain. Coralie porte la baguette tiède. Ensuite, les légumes. Des poireaux. Des tomates.
-papa|L'argent sert aussi aux légumes.
-narrateur|Coralie pose une tomate dans le cabas. Plus loin, il y a des chaussures. Papa montre une paire.
-narrateur|L'argent sert aux chaussures, quand on en a besoin.
-narrateur|Coralie touche le cuir souple. Papa range le reste.
-enfant-f|Le travail de papa sert à acheter pain légumes chaussures. L'argent ne pousse pas tout seul.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Les vitres du hall font des carreaux d'or.
+narrateur|Des pigeons marchent sur une poutre.
+narrateur|Ça sent le foin et le lait.
+narrateur|Une paille craque sous une caisse.
+narrateur|Le toit de verre cliquette un peu.
+narrateur|Papa a fini son travail.
+narrateur|Sa poche de toile est lourde.
+papa|J'ai travaillé, Aniss.
+papa|Avec le travail, on a de l'argent.
+papa|L'argent sert à acheter.
+enfant-m|On achète du fromage ?
+papa|Oui.
+papa|Pour le pain de ce soir.
+narrateur|En ce moment, ils marchent sous le verre.
+narrateur|Aniss tient le bord du cabas.
+narrateur|Le cabas gratte un peu sa jambe.
+narrateur|Un stand aligne des meules.
+narrateur|Des croûtes jaunes brillent.
+enfant-m|Ça sent fort !
+papa|Tu as senti le fromage ?
+narrateur|Aniss se penche vers une meule.
+narrateur|La croûte est rêche sous son doigt.
+enfant-m|Je veux celui-là.
+narrateur|Papa coupe un tout petit bout.
+narrateur|Aniss goûte.
+narrateur|Le goût pique sa langue.
+enfant-m|Il est trop fort !
+papa|Il pique, n'est-ce pas ?
+narrateur|Aniss recule d'un pas.
+narrateur|Ses yeux piquent un peu.
+enfant-m|Je n'en veux plus.
+papa|On prend le doux, alors ?
+narrateur|À côté, une meule est plus claire.
+narrateur|Elle sent le lait, presque rien.
+enfant-m|Celle-là.
+enfant-m|Elle est douce.
+papa|Tu la veux pour le pain ?
+enfant-m|Oui, papa.
+narrateur|Papa sort l'argent de sa poche.
+narrateur|Les pièces sont froides et claires.
+papa|C'est l'argent du travail.
+papa|Il sert à acheter.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1352,7 +1397,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Papa a &lt;emphasis level="moderate"&gt;travail&lt;/emphasis&gt;lé. L'argent sert à quoi ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa a travaillé. L'argent sert à quoi ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1367,7 +1412,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>acheter | le pain | acheter du pain | le travail</t>
+          <t>acheter | le fromage | fromage | acheter du fromage | à acheter</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1382,7 +1427,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>On achète du pain. L'argent sert à quoi ?</t>
+          <t>L'argent sert à acheter. L'argent sert à quoi ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1424,14 +1469,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA3" s="2" t="n">
         <v>0.9</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1507,10 +1552,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Papa a travaillé. L'argent sert à quoi ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Papa a travaillé.
+narrateur|L'argent sert à quoi ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1535,12 +1580,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Coralie a compris. Le travail de papa sert. L'argent sert à acheter. Pain. Légumes. Chaussures.</t>
+          <t>Papa pose les pièces sur le bois. Le bois est taché de lait. On lui tend le fromage doux. Il est enveloppé dans un papier. Le papier craque un peu. Il est à nous ? Oui. On l'a acheté. Merci, Aniss. Tu as choisi le doux. Aniss prend le paquet contre lui. Le fromage est frais, un peu mou. Il ne pique plus. Tu le portes jusqu'à la maison ? Oui. Ils quittent le stand. Une goutte tombe du toit de verre. Elle fait un rond dans la poussière.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Coralie a compris. Le &lt;emphasis level="moderate"&gt;travail&lt;/emphasis&gt; de papa sert. L'argent sert à acheter. Pain. Légumes. Chaussures.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa pose les pièces sur le bois. Le bois est taché de lait. On lui tend le fromage doux. Il est enveloppé dans un papier. Le papier craque un peu. Il est à nous ? Oui. On l'a acheté. Merci, Aniss. Tu as choisi le doux. Aniss prend le paquet contre lui. Le fromage est frais, un peu mou. Il ne pique plus. Tu le portes jusqu'à la maison ? Oui. Ils quittent le stand. Une goutte tombe du toit de verre. Elle fait un rond dans la poussière.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1603,7 +1648,7 @@
         <v>0.96</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1679,10 +1724,26 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Coralie a compris. Le travail de papa sert. L'argent sert à acheter. Pain. Légumes. Chaussures.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Papa pose les pièces sur le bois.
+narrateur|Le bois est taché de lait.
+narrateur|On lui tend le fromage doux.
+narrateur|Il est enveloppé dans un papier.
+narrateur|Le papier craque un peu.
+enfant-m|Il est à nous ?
+papa|Oui.
+papa|On l'a acheté.
+papa|Merci, Aniss.
+papa|Tu as choisi le doux.
+narrateur|Aniss prend le paquet contre lui.
+narrateur|Le fromage est frais, un peu mou.
+enfant-m|Il ne pique plus.
+papa|Tu le portes jusqu'à la maison ?
+enfant-m|Oui.
+narrateur|Ils quittent le stand.
+narrateur|Une goutte tombe du toit de verre.
+narrateur|Elle fait un rond dans la poussière.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1707,12 +1768,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>À la maison, Coralie pose le pain. Papa range les légumes.</t>
+          <t>Dehors, l'air est plus léger. Le cabas tape contre la jambe. Aniss garde le fromage dans ses bras. Tu as encore le paquet ? Oui. Il est frais. Le pain nous attend. La rue sent encore le foin. Une feuille tourne près du caniveau. Ils montent les marches de la maison. La clé fait un petit clic. La table de la cuisine est claire. Le pain est déjà là, tiède. Tu poses le fromage près du pain ? Aniss pose le paquet. Il ouvre le papier, tout doux.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;À la maison, Coralie pose le pain. Papa range les légumes.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Dehors, l'air est plus léger. Le cabas tape contre la jambe. Aniss garde le fromage dans ses bras. Tu as encore le paquet ? Oui. Il est frais. Le pain nous attend. La rue sent encore le foin. Une feuille tourne près du caniveau. Ils montent les marches de la maison. La clé fait un petit clic. La table de la cuisine est claire. Le pain est déjà là, tiède. Tu poses le fromage près du pain ? Aniss pose le paquet. Il ouvre le papier, tout doux.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1775,7 +1836,7 @@
         <v>0.96</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1843,10 +1904,24 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|À la maison, Coralie pose le pain. Papa range les légumes.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Dehors, l'air est plus léger.
+narrateur|Le cabas tape contre la jambe.
+narrateur|Aniss garde le fromage dans ses bras.
+papa|Tu as encore le paquet ?
+enfant-m|Oui.
+enfant-m|Il est frais.
+papa|Le pain nous attend.
+narrateur|La rue sent encore le foin.
+narrateur|Une feuille tourne près du caniveau.
+narrateur|Ils montent les marches de la maison.
+narrateur|La clé fait un petit clic.
+narrateur|La table de la cuisine est claire.
+narrateur|Le pain est déjà là, tiède.
+papa|Tu poses le fromage près du pain ?
+narrateur|Aniss pose le paquet.
+narrateur|Il ouvre le papier, tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1871,12 +1946,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Papa coupe une tranche de pain. Aniss étale le fromage doux. Ça fond un peu, blanc et calme. Il ne pique pas. Bravo. Tu as bien choisi. Aniss croque. Le pain est tiède sous les dents. Le fromage doux reste sur sa langue. Il tient encore le papier vide. Le fromage doux fond encore sur le pain.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa coupe une tranche de pain. Aniss étale le fromage doux. Ça fond un peu, blanc et calme. Il ne pique pas. Bravo. Tu as bien choisi. Aniss croque. Le pain est tiède sous les dents. Le fromage doux reste sur sa langue. Il tient encore le papier vide. Le fromage doux fond encore sur le pain.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1939,7 +2014,7 @@
         <v>0.92</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2011,10 +2086,19 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Papa coupe une tranche de pain.
+narrateur|Aniss étale le fromage doux.
+narrateur|Ça fond un peu, blanc et calme.
+enfant-m|Il ne pique pas.
+papa|Bravo.
+papa|Tu as bien choisi.
+narrateur|Aniss croque.
+narrateur|Le pain est tiède sous les dents.
+narrateur|Le fromage doux reste sur sa langue.
+narrateur|Il tient encore le papier vide.
+narrateur|Le fromage doux fond encore sur le pain.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2033,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2071,6 +2155,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.ARG.001-07.xlsx
+++ b/stories/arbres/ATOM-SOC.ARG.001-07.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>marché</t>
+          <t>marché couvert, hall de verre, stand de fromage</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Coralie, papa</t>
+          <t>Aniss, papa</t>
         </is>
       </c>
     </row>
